--- a/data/trans_orig/IP2004-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2004-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67167</t>
+          <t>67797</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152393</t>
+          <t>152743</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>244728</t>
+          <t>245152</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>250788</t>
+          <t>250769</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>247061</t>
+          <t>246980</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>252383</t>
+          <t>252382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>495216</t>
+          <t>494706</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>502032</t>
+          <t>502088</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13093</t>
+          <t>13385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20476</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>116583</t>
+          <t>116273</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124761</t>
+          <t>124655</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125706</t>
+          <t>125414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134814</t>
+          <t>134619</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>245871</t>
+          <t>245994</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>257524</t>
+          <t>257165</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19571</t>
+          <t>20176</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17199</t>
+          <t>17567</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33104</t>
+          <t>32895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>173843</t>
+          <t>173238</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185172</t>
+          <t>185507</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>187333</t>
+          <t>186814</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>197802</t>
+          <t>197648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>364563</t>
+          <t>364772</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>380468</t>
+          <t>380100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15021</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15049</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29460</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34325</t>
+          <t>34895</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54994</t>
+          <t>55184</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>612709</t>
+          <t>613056</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>627687</t>
+          <t>628141</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>651244</t>
+          <t>650906</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>665655</t>
+          <t>665422</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1268872</t>
+          <t>1268682</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1289541</t>
+          <t>1288971</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,39 +3038,39 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2595</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7223</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2595</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6919</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14189</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>226098</t>
+          <t>225426</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>233969</t>
+          <t>233981</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,42 +3151,42 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>265780</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>261152</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>267669</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>99,03%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>265780</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>261456</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>267674</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>490188</t>
+          <t>490436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>501043</t>
+          <t>500848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>148391</t>
+          <t>147797</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>155032</t>
+          <t>155017</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147367</t>
+          <t>146245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155908</t>
+          <t>155841</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>298059</t>
+          <t>298857</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>309595</t>
+          <t>309532</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18612</t>
+          <t>18378</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14685</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28884</t>
+          <t>28162</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152116</t>
+          <t>152350</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163588</t>
+          <t>164059</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>164602</t>
+          <t>164389</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174601</t>
+          <t>174916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>321131</t>
+          <t>321853</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>336015</t>
+          <t>336077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13929</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29559</t>
+          <t>29592</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>10646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25767</t>
+          <t>25644</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28013</t>
+          <t>28308</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48995</t>
+          <t>49648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>632658</t>
+          <t>632625</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>648288</t>
+          <t>647653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>676389</t>
+          <t>676512</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>691303</t>
+          <t>691510</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1315377</t>
+          <t>1314724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1336359</t>
+          <t>1336064</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>6445</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>203837</t>
+          <t>202932</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>460937</t>
+          <t>461439</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>14598</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20280</t>
+          <t>20415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173949</t>
+          <t>174301</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>183668</t>
+          <t>184021</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>179482</t>
+          <t>180239</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>186635</t>
+          <t>187162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>357191</t>
+          <t>357056</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>369349</t>
+          <t>369429</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13773</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13190</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22727</t>
+          <t>22762</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158283</t>
+          <t>158963</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168187</t>
+          <t>168100</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160858</t>
+          <t>161407</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170564</t>
+          <t>170517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>323376</t>
+          <t>323341</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>336618</t>
+          <t>336528</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26752</t>
+          <t>27149</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17323</t>
+          <t>17999</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21945</t>
+          <t>22538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40238</t>
+          <t>40371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>631885</t>
+          <t>631488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>646158</t>
+          <t>646063</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>683572</t>
+          <t>682896</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>694288</t>
+          <t>694113</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1319294</t>
+          <t>1319161</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1337587</t>
+          <t>1336994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>9730</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>172019</t>
+          <t>171833</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>179853</t>
+          <t>179751</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>331233</t>
+          <t>330710</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>339098</t>
+          <t>338940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10191</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14412</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164980</t>
+          <t>164309</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>171862</t>
+          <t>172056</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>202299</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>210609</t>
+          <t>210426</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>371151</t>
+          <t>371578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>381492</t>
+          <t>381288</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10155</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>14118</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19555</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>265454</t>
+          <t>265303</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>273805</t>
+          <t>273816</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>291692</t>
+          <t>291365</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>301759</t>
+          <t>301926</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>561385</t>
+          <t>561742</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>573728</t>
+          <t>574130</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7966,42 +7966,42 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>17057</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>10765</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>25750</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>2,28%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17057</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>10934</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>26191</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>16155</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34804</t>
+          <t>35730</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>641143</t>
+          <t>642691</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>652100</t>
+          <t>652064</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,47 +8074,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>730408</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>721715</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>736700</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>97,72%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>730408</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>721274</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>736531</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1368732</t>
+          <t>1367806</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1386396</t>
+          <t>1387381</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2004-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2004-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,107 +723,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2970</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3568</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2644</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>84620</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>70169</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>67797</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>67199</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>70767</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,16%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>94,96%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>84620</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>234</t>
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152743</t>
+          <t>152379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>84620</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>84620</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>84620</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>70767</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70767</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>70767</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>84620</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>84620</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>84620</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1071,67 +1071,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>2643</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6544</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>2416</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6282</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5722</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2643</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6051</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>250388</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>246487</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>252382</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>372</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>249018</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>245152</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>250769</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>245712</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>250859</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,04%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>250388</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>246980</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>252382</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>494706</t>
+          <t>494789</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>502088</t>
+          <t>502034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253031</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253031</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253031</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>376</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>251434</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>251434</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>251434</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253031</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253031</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253031</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7626</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4127</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12788</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6017</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2893</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11275</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2915</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10894</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,72%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7626</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4180</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13385</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>21361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>131173</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>126011</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>134672</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>121531</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>116273</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>124655</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>116654</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>124633</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,28%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,16%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>131173</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>125414</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>134619</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,51%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>245994</t>
+          <t>244986</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>257165</t>
+          <t>257637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>138799</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>138799</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>138799</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>138799</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>138799</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>138799</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11279</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6245</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17582</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>13021</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7907</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20176</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8214</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19822</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,73%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11279</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6606</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>17440</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17567</t>
+          <t>17400</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32895</t>
+          <t>33068</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>192975</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>186672</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>198009</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,48%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>180393</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>173238</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>185507</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>173592</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>185200</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,27%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,57%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>192975</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>186814</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>197648</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,48%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>364772</t>
+          <t>364599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>380100</t>
+          <t>380267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204254</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204254</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204254</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>193414</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>193414</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>193414</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204254</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204254</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204254</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2100,67 +2100,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>21548</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15280</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29635</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>22051</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15021</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>30106</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>15223</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>30597</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,43%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>21548</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>15282</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>29798</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34895</t>
+          <t>34429</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55184</t>
+          <t>54328</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>659156</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>651069</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>665424</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,65%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,76%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>927</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>621111</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>613056</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>628141</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>612565</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>627939</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,57%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>990</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>659156</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>650906</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>665422</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1268682</t>
+          <t>1269538</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1288971</t>
+          <t>1289437</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>680704</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>680704</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>680704</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>960</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>643162</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>643162</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>643162</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1023</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>680704</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>680704</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>680704</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2783,47 +2783,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>98870</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>98870</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>98870</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>98870</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2595</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7043</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5208</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2269</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10824</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2236</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10353</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,2%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2595</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7223</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>265780</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>261332</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>267674</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>333</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>231042</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>225426</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>233981</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>225897</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>234014</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>265780</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>261152</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>267669</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>490436</t>
+          <t>490751</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>500848</t>
+          <t>500854</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268375</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268375</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268375</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268375</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268375</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268375</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6047</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2688</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11425</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3984</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8571</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6047</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2730</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12326</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>16163</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>152524</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>147146</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>155883</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>152384</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>147797</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>155017</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>148058</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>154456</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,45%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,52%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>152524</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>146245</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>155841</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>298857</t>
+          <t>298776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>309532</t>
+          <t>309338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156368</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156368</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156368</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8477</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4709</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14989</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11763</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18378</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7238</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18338</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,89%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8477</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4371</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>14898</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28162</t>
+          <t>28783</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>170810</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>164298</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>174578</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>158965</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>152350</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>164059</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>152390</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>163490</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,11%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>170810</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>164389</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>174916</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,27%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>321853</t>
+          <t>321232</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>336077</t>
+          <t>336383</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179287</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179287</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179287</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170728</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170728</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170728</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179287</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179287</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179287</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17120</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11243</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>26097</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>20955</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14564</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>29592</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>14641</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>29159</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17120</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>10646</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>25644</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28308</t>
+          <t>29207</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49648</t>
+          <t>49547</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>979</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>685036</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>676059</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>690913</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>924</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>641262</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>632625</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>647653</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>633058</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>647576</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,84%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,53%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>979</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>685036</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>676512</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>691510</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,56%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1314724</t>
+          <t>1314825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1336064</t>
+          <t>1335165</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>702156</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>702156</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>702156</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>662217</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>662217</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>662217</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>702156</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>702156</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>702156</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4730,47 +4730,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>87859</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>87859</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>87859</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>87859</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,107 +4960,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1934</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6891</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6281</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>6361</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1934</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>6445</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -5073,74 +5073,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>207889</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>202932</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>203542</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>209823</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,08%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,01%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>709</t>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>461439</t>
+          <t>461523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>209823</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>209823</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>209823</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4147</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1412</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8428</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8893</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4878</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14598</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4903</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15561</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,71%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4147</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1410</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8333</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20415</t>
+          <t>19567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>184425</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>180144</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>187160</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,8%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>180006</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>174301</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>184021</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>173338</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>183996</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,27%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>184425</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>180239</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>187162</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>357056</t>
+          <t>357904</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>369429</t>
+          <t>369072</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3640</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12818</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7765</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3956</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13093</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3821</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13382</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,51%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7301</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3531</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12641</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22762</t>
+          <t>23276</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>166747</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>161230</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>170408</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,8%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>164291</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>158963</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>168100</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>158674</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>168235</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>166747</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>161407</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>170517</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>323341</t>
+          <t>322827</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>336528</t>
+          <t>336667</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172056</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172056</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172056</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11449</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6984</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17556</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>18592</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12574</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>27149</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>12341</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>26686</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>11449</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6782</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>17999</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22538</t>
+          <t>21326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40371</t>
+          <t>39957</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>689446</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>683339</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>693911</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>961</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>640045</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>631488</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>646063</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>631951</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>646296</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,18%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,88%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>984</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>689446</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>682896</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>694113</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1319161</t>
+          <t>1319575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1336994</t>
+          <t>1338206</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>988</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>658637</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>658637</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>658637</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>48405</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>44563</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>47929</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>176</t>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>96334</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>48405</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>48405</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>48405</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>96334</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>96334</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96334</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,107 +6907,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4156</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1614</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9290</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4571</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9730</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -7020,74 +7020,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>152588</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>147454</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>155130</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>159136</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>145025</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>176992</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>171833</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>179751</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>94,64%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>525</t>
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>336128</t>
+          <t>297613</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330710</t>
+          <t>292169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>338940</t>
+          <t>300280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156744</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156744</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156744</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159136</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159136</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159136</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181563</t>
+          <t>145025</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181563</t>
+          <t>145025</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181563</t>
+          <t>145025</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>340699</t>
+          <t>301769</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>340699</t>
+          <t>301769</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>340699</t>
+          <t>301769</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4659</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1757</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9954</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3242</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8763</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13985</t>
+          <t>14242</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>195467</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>190172</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>198369</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,03%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>169830</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>164309</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>172056</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>207605</t>
+          <t>171329</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>166743</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>210426</t>
+          <t>173561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>377436</t>
+          <t>366796</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>371578</t>
+          <t>360556</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>381288</t>
+          <t>371082</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6812</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3369</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12979</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4408</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1642</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10155</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14118</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>12009</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19198</t>
+          <t>18220</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>285833</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>279666</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>289276</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>336</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>271050</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>265303</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>273816</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,31%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>297882</t>
+          <t>251941</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>291365</t>
+          <t>246646</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>301926</t>
+          <t>254964</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>568931</t>
+          <t>537774</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>561742</t>
+          <t>530978</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>574130</t>
+          <t>542347</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15627</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10377</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23077</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>7651</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>7955</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>4007</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13380</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17057</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>10765</t>
-        </is>
-      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25750</t>
+          <t>14589</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>23583</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>15940</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35730</t>
+          <t>34073</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>673563</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>666113</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>678813</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,65%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>910</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>648420</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>642691</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>652064</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>730408</t>
+          <t>612859</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>721715</t>
+          <t>606225</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>736700</t>
+          <t>616807</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1378829</t>
+          <t>1286421</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1367806</t>
+          <t>1275931</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1387381</t>
+          <t>1294064</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>921</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
